--- a/data_dev/對照表.xlsx
+++ b/data_dev/對照表.xlsx
@@ -620,7 +620,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::米咖色, M</t>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::灰湖綠, M</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】黑灰色, XL ➜建議80-85KG</t>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::煙粉色, M</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -657,24 +657,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
+          <t>天山棉麻衣物整理摺疊收納箱[中號40L]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HFA01019-DN-XL</t>
+          <t>HGI03024-40L</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HFA01019</t>
+          <t>HGI03024</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, L ➜建議70-75KG</t>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::米咖色, M</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -684,12 +684,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[深藍M]</t>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HFA01019-DN-M</t>
+          <t>HFA01019-DN-XL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,7 +701,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, L ➜建議70-75KG</t>
+          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::紫羅蘭, M</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -711,12 +711,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[杏色M]</t>
+          <t>厚磅撞色圓領短版修身短袖T恤[杏色XL]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HFA01019-BG-M</t>
+          <t>HFA01019-BG-XL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,7 +728,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, M ➜建議60-65KG</t>
+          <t>超柔順莫代爾棉☁️高質感彩紗條紋男性四角內褲::【素色】黑灰色, XL ➜建議80-85KG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[杏色M]</t>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HFA01019-BG-M</t>
+          <t>HFA01019-DN-XL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -782,7 +782,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::酒紅色, M ➜建議60-65KG</t>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -792,24 +792,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>M型短頸膚感防滑衣架[燕麥白]</t>
+          <t>厚磅撞色圓領短版修身短袖T恤[杏色M]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HGI03023-WH</t>
+          <t>HFA01019-BG-M</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HGI03023</t>
+          <t>HFA01019</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, M ➜建議60-65KG</t>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::白色, M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
+          <t>厚磅撞色圓領短版修身短袖T恤[杏色M]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HFA01019-DN-XL</t>
+          <t>HFA01019-BG-M</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -863,7 +863,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::灰湖綠, M</t>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::酒紅色, M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -873,24 +873,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
+          <t>M型短頸膚感防滑衣架[燕麥白]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HFA01019-DN-XL</t>
+          <t>HGI03023-WH</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HFA01019</t>
+          <t>HGI03023</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::紫羅蘭, M</t>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, L ➜建議70-75KG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -900,12 +900,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>厚磅撞色圓領短版修身短袖T恤[杏色XL]</t>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍M]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HFA01019-BG-XL</t>
+          <t>HFA01019-DN-M</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,7 +917,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>真好穿🌷不捲邊不夾臀🍑裸感60S莫代爾超舒適加寬邊中高腰內褲三角褲::煙粉色, M</t>
+          <t>超輕薄涼爽無痕零觸感！高品質舒適彈力冰絲四角內褲::黑色, M ➜建議60-65KG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -927,17 +927,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>天山棉麻衣物整理摺疊收納箱[中號40L]</t>
+          <t>厚磅撞色圓領短版修身短袖T恤[深藍XL]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HGI03024-40L</t>
+          <t>HFA01019-DN-XL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HGI03024</t>
+          <t>HFA01019</t>
         </is>
       </c>
     </row>
